--- a/tests/fixtures/excel_espera.xlsx
+++ b/tests/fixtures/excel_espera.xlsx
@@ -184,7 +184,7 @@
     <t>Fernanda Cruz</t>
   </si>
   <si>
-    <t>Matias Leon</t>
+    <t>Marco León</t>
   </si>
   <si>
     <t>Isidora Silva</t>
@@ -238,10 +238,10 @@
     <t>AFT Familia</t>
   </si>
   <si>
-    <t>04/07/2008</t>
-  </si>
-  <si>
-    <t>08/08/2008</t>
+    <t>09/07/2008</t>
+  </si>
+  <si>
+    <t>13/08/2008</t>
   </si>
   <si>
     <t>10</t>
@@ -325,21 +325,29 @@
     <t>17171717-1</t>
   </si>
   <si>
-    <t>20/06/2026</t>
-  </si>
-  <si>
-    <t>05/07/2026</t>
-  </si>
-  <si>
-    <t>08/07/2026</t>
+    <t>25/06/2026</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -355,7 +363,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -363,12 +371,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,37 +693,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
